--- a/verification/model_verification_results_300_buses.xlsx
+++ b/verification/model_verification_results_300_buses.xlsx
@@ -618,19 +618,19 @@
         <v>100</v>
       </c>
       <c r="C2">
-        <v>90.8720765211738</v>
+        <v>26.97825475337033</v>
       </c>
       <c r="D2">
-        <v>84.12194851482612</v>
+        <v>0.1518579937604134</v>
       </c>
       <c r="E2">
-        <v>80.16131301885606</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>80.19454562850817</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>80.05863271205718</v>
+        <v>0.002940327621058374</v>
       </c>
       <c r="H2">
         <v>100</v>
@@ -654,37 +654,37 @@
         <v>100</v>
       </c>
       <c r="O2">
-        <v>71.777243939874</v>
+        <v>67.45683780789932</v>
       </c>
       <c r="P2">
-        <v>44.46925376274186</v>
+        <v>35.89158166039648</v>
       </c>
       <c r="Q2">
-        <v>25.37928161378077</v>
+        <v>13.70537011602996</v>
       </c>
       <c r="R2">
-        <v>16.77825417076159</v>
+        <v>3.724152995806007</v>
       </c>
       <c r="S2">
-        <v>13.39455486191918</v>
+        <v>0</v>
       </c>
       <c r="T2">
         <v>100</v>
       </c>
       <c r="U2">
-        <v>79.36422889578546</v>
+        <v>62.13656387144314</v>
       </c>
       <c r="V2">
-        <v>65.9494791137427</v>
+        <v>38.25560472262411</v>
       </c>
       <c r="W2">
-        <v>55.61745354693258</v>
+        <v>20.27025189504208</v>
       </c>
       <c r="X2">
-        <v>47.25713866266791</v>
+        <v>5.600164449024823</v>
       </c>
       <c r="Y2">
-        <v>43.37411734077338</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -695,19 +695,19 @@
         <v>100</v>
       </c>
       <c r="C3">
-        <v>99.68624110256437</v>
+        <v>13.32791003979115</v>
       </c>
       <c r="D3">
-        <v>99.36987199100747</v>
+        <v>0.03059998284151059</v>
       </c>
       <c r="E3">
-        <v>99.199594269805</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>99.09685351397751</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>99.01072264800953</v>
+        <v>0.0003444760040748736</v>
       </c>
       <c r="H3">
         <v>100</v>
@@ -731,37 +731,37 @@
         <v>100</v>
       </c>
       <c r="O3">
-        <v>66.17339679542337</v>
+        <v>64.60508491793659</v>
       </c>
       <c r="P3">
-        <v>34.14855082373625</v>
+        <v>29.9050202796302</v>
       </c>
       <c r="Q3">
-        <v>13.90685711128604</v>
+        <v>8.579944220376333</v>
       </c>
       <c r="R3">
-        <v>6.920572065502855</v>
+        <v>1.907730413713536</v>
       </c>
       <c r="S3">
-        <v>4.301345853666675</v>
+        <v>0</v>
       </c>
       <c r="T3">
         <v>100</v>
       </c>
       <c r="U3">
-        <v>69.85493260833799</v>
+        <v>56.40268909947284</v>
       </c>
       <c r="V3">
-        <v>51.63961598859598</v>
+        <v>32.66786183293418</v>
       </c>
       <c r="W3">
-        <v>38.47170956750799</v>
+        <v>16.32053886416679</v>
       </c>
       <c r="X3">
-        <v>28.24738862661738</v>
+        <v>3.648675116569349</v>
       </c>
       <c r="Y3">
-        <v>22.69401259376958</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -772,73 +772,73 @@
         <v>100</v>
       </c>
       <c r="C4">
-        <v>90.85800707370167</v>
+        <v>45.03880124231288</v>
       </c>
       <c r="D4">
-        <v>84.09083113744718</v>
+        <v>12.80888798148904</v>
       </c>
       <c r="E4">
-        <v>80.08627680075247</v>
+        <v>3.234865189254736</v>
       </c>
       <c r="F4">
-        <v>80.11031146667061</v>
+        <v>0.4198640137594813</v>
       </c>
       <c r="G4">
-        <v>79.97500334745347</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <v>100</v>
       </c>
       <c r="I4">
-        <v>68.27101367239725</v>
+        <v>67.44462707216334</v>
       </c>
       <c r="J4">
-        <v>46.32973136707214</v>
+        <v>45.14917134514261</v>
       </c>
       <c r="K4">
-        <v>31.85165045027288</v>
+        <v>30.4970855689092</v>
       </c>
       <c r="L4">
-        <v>21.7899875910132</v>
+        <v>20.94189702280335</v>
       </c>
       <c r="M4">
-        <v>14.24004710962656</v>
+        <v>13.90540817295175</v>
       </c>
       <c r="N4">
         <v>100</v>
       </c>
       <c r="O4">
-        <v>68.04897726603069</v>
+        <v>68.13121730134017</v>
       </c>
       <c r="P4">
-        <v>36.13543080610487</v>
+        <v>36.26678188903973</v>
       </c>
       <c r="Q4">
-        <v>12.41378063981925</v>
+        <v>12.47685855169907</v>
       </c>
       <c r="R4">
-        <v>2.195558231263028</v>
+        <v>2.259985576265866</v>
       </c>
       <c r="S4">
-        <v>0.04153051930109267</v>
+        <v>0.04121947797934163</v>
       </c>
       <c r="T4">
         <v>100</v>
       </c>
       <c r="U4">
-        <v>55.37228118303256</v>
+        <v>54.06234453111526</v>
       </c>
       <c r="V4">
-        <v>30.44488691655544</v>
+        <v>29.46518537592279</v>
       </c>
       <c r="W4">
-        <v>11.84637904526001</v>
+        <v>11.68046656551341</v>
       </c>
       <c r="X4">
-        <v>2.292936425104614</v>
+        <v>2.224676021386983</v>
       </c>
       <c r="Y4">
-        <v>0.05577226093074559</v>
+        <v>0.05270002542300268</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -849,73 +849,73 @@
         <v>100</v>
       </c>
       <c r="C5">
-        <v>99.63156550986287</v>
+        <v>44.22057388987211</v>
       </c>
       <c r="D5">
-        <v>99.34882585010084</v>
+        <v>12.40967917186739</v>
       </c>
       <c r="E5">
-        <v>99.10154248836054</v>
+        <v>3.002343305892904</v>
       </c>
       <c r="F5">
-        <v>98.97531112855049</v>
+        <v>0.3534049951610364</v>
       </c>
       <c r="G5">
-        <v>98.8812463071519</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>100</v>
       </c>
       <c r="I5">
-        <v>67.06549821341291</v>
+        <v>66.11050930902638</v>
       </c>
       <c r="J5">
-        <v>42.6535403736006</v>
+        <v>42.19922082133788</v>
       </c>
       <c r="K5">
-        <v>26.73016494773839</v>
+        <v>25.76534734906389</v>
       </c>
       <c r="L5">
-        <v>16.07208665822622</v>
+        <v>15.64667542909792</v>
       </c>
       <c r="M5">
-        <v>8.940462549678726</v>
+        <v>8.871618321949429</v>
       </c>
       <c r="N5">
         <v>100</v>
       </c>
       <c r="O5">
-        <v>66.33068906565526</v>
+        <v>66.46243915435139</v>
       </c>
       <c r="P5">
-        <v>29.81370246727759</v>
+        <v>30.13027829546609</v>
       </c>
       <c r="Q5">
-        <v>5.275752982300062</v>
+        <v>5.336812044224095</v>
       </c>
       <c r="R5">
-        <v>0.8718658144636661</v>
+        <v>0.8848649834688691</v>
       </c>
       <c r="S5">
-        <v>0.005654977899858364</v>
+        <v>0.005604695285853352</v>
       </c>
       <c r="T5">
         <v>100</v>
       </c>
       <c r="U5">
-        <v>45.66621887870044</v>
+        <v>44.09429554721823</v>
       </c>
       <c r="V5">
-        <v>20.2279848234634</v>
+        <v>19.25593334267645</v>
       </c>
       <c r="W5">
-        <v>9.494872231789298</v>
+        <v>8.999988211702721</v>
       </c>
       <c r="X5">
-        <v>2.397675315523206</v>
+        <v>2.261287219428952</v>
       </c>
       <c r="Y5">
-        <v>0.01314576475547876</v>
+        <v>0.01225080092343052</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -926,73 +926,73 @@
         <v>100</v>
       </c>
       <c r="C6">
-        <v>90.85800707370167</v>
+        <v>45.03880124231288</v>
       </c>
       <c r="D6">
-        <v>84.09083113744718</v>
+        <v>12.80888798148904</v>
       </c>
       <c r="E6">
-        <v>80.0936016989364</v>
+        <v>3.234865189254736</v>
       </c>
       <c r="F6">
-        <v>80.1268062373933</v>
+        <v>0.4198640137594813</v>
       </c>
       <c r="G6">
-        <v>79.99100812498706</v>
+        <v>0.0003318260700100226</v>
       </c>
       <c r="H6">
         <v>100</v>
       </c>
       <c r="I6">
-        <v>68.27101367239725</v>
+        <v>67.44462707216334</v>
       </c>
       <c r="J6">
-        <v>46.32973136707214</v>
+        <v>45.14917134514261</v>
       </c>
       <c r="K6">
-        <v>31.85165045027288</v>
+        <v>30.4970855689092</v>
       </c>
       <c r="L6">
-        <v>21.7899875910132</v>
+        <v>20.94189702280335</v>
       </c>
       <c r="M6">
-        <v>14.24004710962656</v>
+        <v>13.90540817295175</v>
       </c>
       <c r="N6">
         <v>100</v>
       </c>
       <c r="O6">
-        <v>71.777243939874</v>
+        <v>67.45683780789932</v>
       </c>
       <c r="P6">
-        <v>44.46925376274186</v>
+        <v>35.89158166039648</v>
       </c>
       <c r="Q6">
-        <v>25.37928161378077</v>
+        <v>13.70537011602996</v>
       </c>
       <c r="R6">
-        <v>16.77825417076159</v>
+        <v>3.724152995806007</v>
       </c>
       <c r="S6">
-        <v>13.39455486191918</v>
+        <v>0.0244322274296326</v>
       </c>
       <c r="T6">
         <v>100</v>
       </c>
       <c r="U6">
-        <v>79.36422889578546</v>
+        <v>62.13656387144314</v>
       </c>
       <c r="V6">
-        <v>65.9494791137427</v>
+        <v>38.25560472262411</v>
       </c>
       <c r="W6">
-        <v>55.61745354693258</v>
+        <v>20.27025189504208</v>
       </c>
       <c r="X6">
-        <v>47.25713866266791</v>
+        <v>5.600164449024823</v>
       </c>
       <c r="Y6">
-        <v>43.37411734077338</v>
+        <v>0.02814407996812706</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1003,73 +1003,73 @@
         <v>100</v>
       </c>
       <c r="C7">
-        <v>99.65888384195003</v>
+        <v>37.765125352209</v>
       </c>
       <c r="D7">
-        <v>99.35933577329197</v>
+        <v>9.822899654348527</v>
       </c>
       <c r="E7">
-        <v>99.15054087788062</v>
+        <v>2.374962045228559</v>
       </c>
       <c r="F7">
-        <v>99.03605044768281</v>
+        <v>0.279556121531554</v>
       </c>
       <c r="G7">
-        <v>98.94594803474416</v>
+        <v>7.19830436158564E-05</v>
       </c>
       <c r="H7">
         <v>100</v>
       </c>
       <c r="I7">
-        <v>67.05019414748547</v>
+        <v>66.08046388638249</v>
       </c>
       <c r="J7">
-        <v>42.6438070142533</v>
+        <v>42.18003809999476</v>
       </c>
       <c r="K7">
-        <v>26.72406523600122</v>
+        <v>25.75363505985839</v>
       </c>
       <c r="L7">
-        <v>16.06841907533543</v>
+        <v>15.63956283770735</v>
       </c>
       <c r="M7">
-        <v>8.93842237355349</v>
+        <v>8.867585503835249</v>
       </c>
       <c r="N7">
         <v>100</v>
       </c>
       <c r="O7">
-        <v>66.17522546724528</v>
+        <v>65.35232041262755</v>
       </c>
       <c r="P7">
-        <v>34.09789130096387</v>
+        <v>29.99564752613825</v>
       </c>
       <c r="Q7">
-        <v>13.80598281556214</v>
+        <v>7.275198049093137</v>
       </c>
       <c r="R7">
-        <v>6.849879016401314</v>
+        <v>1.496220764108806</v>
       </c>
       <c r="S7">
-        <v>4.251140431290003</v>
+        <v>0.002254828341653824</v>
       </c>
       <c r="T7">
         <v>100</v>
       </c>
       <c r="U7">
-        <v>69.71870438272521</v>
+        <v>52.58143890208298</v>
       </c>
       <c r="V7">
-        <v>51.46271249951132</v>
+        <v>28.50400463398067</v>
       </c>
       <c r="W7">
-        <v>38.30852067073391</v>
+        <v>14.04780854274364</v>
       </c>
       <c r="X7">
-        <v>28.10180872148817</v>
+        <v>3.21794785596537</v>
       </c>
       <c r="Y7">
-        <v>22.56627805082064</v>
+        <v>0.003803370682496029</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1080,37 +1080,37 @@
         <v>100</v>
       </c>
       <c r="C8">
-        <v>56.79062326819956</v>
+        <v>40.70904866404123</v>
       </c>
       <c r="D8">
-        <v>19.84078008056273</v>
+        <v>10.73846208494886</v>
       </c>
       <c r="E8">
-        <v>5.3080803059345</v>
+        <v>2.692441953161806</v>
       </c>
       <c r="F8">
-        <v>1.059093423818989</v>
+        <v>0.291723681752957</v>
       </c>
       <c r="G8">
-        <v>0.1956311467615071</v>
+        <v>0.06158661361141513</v>
       </c>
       <c r="H8">
         <v>100</v>
       </c>
       <c r="I8">
-        <v>52.86302354346276</v>
+        <v>57.82687393949509</v>
       </c>
       <c r="J8">
-        <v>19.7772338349018</v>
+        <v>25.00129148138876</v>
       </c>
       <c r="K8">
-        <v>12.19356318917136</v>
+        <v>11.63619764036416</v>
       </c>
       <c r="L8">
-        <v>6.594215600994663</v>
+        <v>6.576968316981192</v>
       </c>
       <c r="M8">
-        <v>5.574743824089508</v>
+        <v>4.488665677855532</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1121,37 +1121,37 @@
         <v>100</v>
       </c>
       <c r="C9">
-        <v>56.0333358780053</v>
+        <v>39.40140507466875</v>
       </c>
       <c r="D9">
-        <v>20.42558763735128</v>
+        <v>9.715727449239463</v>
       </c>
       <c r="E9">
-        <v>6.655146155490262</v>
+        <v>2.299198653609616</v>
       </c>
       <c r="F9">
-        <v>1.727439117572225</v>
+        <v>0.3386581947064218</v>
       </c>
       <c r="G9">
-        <v>0.4803314133261555</v>
+        <v>0.05939005202066612</v>
       </c>
       <c r="H9">
         <v>100</v>
       </c>
       <c r="I9">
-        <v>58.68824998606195</v>
+        <v>57.79682310332424</v>
       </c>
       <c r="J9">
-        <v>29.65368429982144</v>
+        <v>30.22542724754938</v>
       </c>
       <c r="K9">
-        <v>15.24048322860045</v>
+        <v>14.60837242046158</v>
       </c>
       <c r="L9">
-        <v>8.913994223750009</v>
+        <v>7.791765184856629</v>
       </c>
       <c r="M9">
-        <v>4.416510214160628</v>
+        <v>3.806841087311522</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1162,37 +1162,37 @@
         <v>100</v>
       </c>
       <c r="C10">
-        <v>56.73937011726158</v>
+        <v>8.51915791216109</v>
       </c>
       <c r="D10">
-        <v>19.7430940855784</v>
+        <v>1.275384085229664</v>
       </c>
       <c r="E10">
-        <v>5.450343047771423</v>
+        <v>2.137448244974365</v>
       </c>
       <c r="F10">
-        <v>1.196908276579884</v>
+        <v>0.7511836079449951</v>
       </c>
       <c r="G10">
-        <v>0.1056978470991946</v>
+        <v>0.2023378987587367</v>
       </c>
       <c r="H10">
         <v>100</v>
       </c>
       <c r="I10">
-        <v>25.59431626471161</v>
+        <v>26.35054754148156</v>
       </c>
       <c r="J10">
-        <v>18.43816205329555</v>
+        <v>17.92438145906429</v>
       </c>
       <c r="K10">
-        <v>16.56037171655513</v>
+        <v>15.98610242693555</v>
       </c>
       <c r="L10">
-        <v>14.8898460248189</v>
+        <v>14.20168587651031</v>
       </c>
       <c r="M10">
-        <v>13.33069266415042</v>
+        <v>12.51135346042444</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1203,37 +1203,37 @@
         <v>100</v>
       </c>
       <c r="C11">
-        <v>55.69259223407337</v>
+        <v>17.57301202990305</v>
       </c>
       <c r="D11">
-        <v>20.07568189731376</v>
+        <v>1.646642347579009</v>
       </c>
       <c r="E11">
-        <v>6.631244550299329</v>
+        <v>1.388832139979951</v>
       </c>
       <c r="F11">
-        <v>1.631796819072564</v>
+        <v>0.4533951079864993</v>
       </c>
       <c r="G11">
-        <v>0.4087106225124602</v>
+        <v>0.1186780427155819</v>
       </c>
       <c r="H11">
         <v>100</v>
       </c>
       <c r="I11">
-        <v>34.45859303247445</v>
+        <v>25.02895676380206</v>
       </c>
       <c r="J11">
-        <v>13.57152649262658</v>
+        <v>12.02299109405701</v>
       </c>
       <c r="K11">
-        <v>7.407127783561604</v>
+        <v>6.525569095782415</v>
       </c>
       <c r="L11">
-        <v>5.70392599003464</v>
+        <v>5.079490193978824</v>
       </c>
       <c r="M11">
-        <v>5.022553745286264</v>
+        <v>4.412552801675345</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1244,37 +1244,37 @@
         <v>100</v>
       </c>
       <c r="C12">
-        <v>56.79062326819956</v>
+        <v>40.70904866404123</v>
       </c>
       <c r="D12">
-        <v>19.84078008056273</v>
+        <v>10.73846208494886</v>
       </c>
       <c r="E12">
-        <v>5.441222336608444</v>
+        <v>2.692441953161806</v>
       </c>
       <c r="F12">
-        <v>1.19490534674894</v>
+        <v>0.2983292862631295</v>
       </c>
       <c r="G12">
-        <v>0.1956311467615071</v>
+        <v>0.08035761201686838</v>
       </c>
       <c r="H12">
         <v>100</v>
       </c>
       <c r="I12">
-        <v>52.86302354346276</v>
+        <v>57.82687393949509</v>
       </c>
       <c r="J12">
-        <v>19.7772338349018</v>
+        <v>25.00129148138876</v>
       </c>
       <c r="K12">
-        <v>12.19356318917136</v>
+        <v>11.63619764036416</v>
       </c>
       <c r="L12">
-        <v>9.670121809017258</v>
+        <v>7.106529498097218</v>
       </c>
       <c r="M12">
-        <v>8.657538946073505</v>
+        <v>6.260686456576864</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1285,37 +1285,37 @@
         <v>100</v>
       </c>
       <c r="C13">
-        <v>55.86453020358145</v>
+        <v>32.19107710965361</v>
       </c>
       <c r="D13">
-        <v>20.25224358920743</v>
+        <v>7.0503577420505</v>
       </c>
       <c r="E13">
-        <v>6.64330537478158</v>
+        <v>1.998487295208045</v>
       </c>
       <c r="F13">
-        <v>1.680058070871081</v>
+        <v>0.3765578916281137</v>
       </c>
       <c r="G13">
-        <v>0.4448508035016775</v>
+        <v>0.07897396190515173</v>
       </c>
       <c r="H13">
         <v>100</v>
       </c>
       <c r="I13">
-        <v>51.03145004928837</v>
+        <v>48.10793778058466</v>
       </c>
       <c r="J13">
-        <v>24.57157205769837</v>
+        <v>24.8432869015667</v>
       </c>
       <c r="K13">
-        <v>12.76506842702145</v>
+        <v>12.21842789450983</v>
       </c>
       <c r="L13">
-        <v>7.899582358417382</v>
+        <v>6.98979302105928</v>
       </c>
       <c r="M13">
-        <v>4.60802535307416</v>
+        <v>3.985939641491202</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1326,37 +1326,37 @@
         <v>100</v>
       </c>
       <c r="C14">
-        <v>54.07677769202014</v>
+        <v>54.25933930036209</v>
       </c>
       <c r="D14">
-        <v>16.45385325219773</v>
+        <v>16.58870885455906</v>
       </c>
       <c r="E14">
-        <v>4.157261966664088</v>
+        <v>4.168740442759014</v>
       </c>
       <c r="F14">
-        <v>0.01256560757982508</v>
+        <v>0.01250384697698229</v>
       </c>
       <c r="G14">
-        <v>0.00216674114139019</v>
+        <v>0.002193239942563582</v>
       </c>
       <c r="H14">
         <v>100</v>
       </c>
       <c r="I14">
-        <v>82.08730961368981</v>
+        <v>80.44398047453002</v>
       </c>
       <c r="J14">
-        <v>66.94420332373974</v>
+        <v>65.30171424180433</v>
       </c>
       <c r="K14">
-        <v>53.34117007871352</v>
+        <v>51.9220443080856</v>
       </c>
       <c r="L14">
-        <v>41.40541325840662</v>
+        <v>40.04864187280581</v>
       </c>
       <c r="M14">
-        <v>33.38645912559037</v>
+        <v>31.65085930747492</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1367,37 +1367,37 @@
         <v>100</v>
       </c>
       <c r="C15">
-        <v>51.37788400187232</v>
+        <v>51.57750444940856</v>
       </c>
       <c r="D15">
-        <v>13.30455790399549</v>
+        <v>13.51656440391835</v>
       </c>
       <c r="E15">
-        <v>1.272531882856283</v>
+        <v>1.269244096602614</v>
       </c>
       <c r="F15">
-        <v>0.004254910225866799</v>
+        <v>0.004227940510514463</v>
       </c>
       <c r="G15">
-        <v>0.0003999779683785884</v>
+        <v>0.0004232798703858067</v>
       </c>
       <c r="H15">
         <v>100</v>
       </c>
       <c r="I15">
-        <v>50.44013505906732</v>
+        <v>50.0573200276109</v>
       </c>
       <c r="J15">
-        <v>27.94160227976815</v>
+        <v>26.06030060149212</v>
       </c>
       <c r="K15">
-        <v>17.22770011441829</v>
+        <v>15.47617101404905</v>
       </c>
       <c r="L15">
-        <v>11.23762850252215</v>
+        <v>9.979319697404296</v>
       </c>
       <c r="M15">
-        <v>9.008430405610204</v>
+        <v>7.859458216638495</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1408,37 +1408,37 @@
         <v>100</v>
       </c>
       <c r="C16">
-        <v>53.32606125166445</v>
+        <v>53.04880101321642</v>
       </c>
       <c r="D16">
-        <v>30.99747536617843</v>
+        <v>30.74628634584285</v>
       </c>
       <c r="E16">
-        <v>11.59462405681314</v>
+        <v>11.51655663506677</v>
       </c>
       <c r="F16">
-        <v>3.728152685308478</v>
+        <v>3.697030198730114</v>
       </c>
       <c r="G16">
-        <v>1.844722592099423</v>
+        <v>1.82116674170415</v>
       </c>
       <c r="H16">
         <v>100</v>
       </c>
       <c r="I16">
-        <v>77.22942606352436</v>
+        <v>76.82844899079002</v>
       </c>
       <c r="J16">
-        <v>55.57154280818965</v>
+        <v>55.18088410006043</v>
       </c>
       <c r="K16">
-        <v>42.7859106479081</v>
+        <v>41.55850243076583</v>
       </c>
       <c r="L16">
-        <v>30.61119414168124</v>
+        <v>29.55610010043041</v>
       </c>
       <c r="M16">
-        <v>19.52675669331749</v>
+        <v>18.53469098744901</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1449,37 +1449,37 @@
         <v>100</v>
       </c>
       <c r="C17">
-        <v>55.99595712625202</v>
+        <v>55.88341252788539</v>
       </c>
       <c r="D17">
-        <v>26.81891881595865</v>
+        <v>26.92580457612378</v>
       </c>
       <c r="E17">
-        <v>8.452018766911989</v>
+        <v>8.409268211153313</v>
       </c>
       <c r="F17">
-        <v>2.212501916078281</v>
+        <v>2.19975705021551</v>
       </c>
       <c r="G17">
-        <v>0.5666155494761238</v>
+        <v>0.5602716101479152</v>
       </c>
       <c r="H17">
         <v>100</v>
       </c>
       <c r="I17">
-        <v>73.11291550652368</v>
+        <v>72.46751468627409</v>
       </c>
       <c r="J17">
-        <v>49.96805205488666</v>
+        <v>49.19279735484754</v>
       </c>
       <c r="K17">
-        <v>31.82160126607565</v>
+        <v>30.9426558564153</v>
       </c>
       <c r="L17">
-        <v>17.25407483608534</v>
+        <v>16.58782571552613</v>
       </c>
       <c r="M17">
-        <v>7.782001335403986</v>
+        <v>7.227347802446525</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1490,52 +1490,52 @@
         <v>100</v>
       </c>
       <c r="C18">
-        <v>53.32606125166445</v>
+        <v>53.04880101321642</v>
       </c>
       <c r="D18">
-        <v>30.99747536617843</v>
+        <v>30.74628634584285</v>
       </c>
       <c r="E18">
-        <v>11.59462405681314</v>
+        <v>11.51655663506677</v>
       </c>
       <c r="F18">
-        <v>3.728152685308478</v>
+        <v>3.697030198730114</v>
       </c>
       <c r="G18">
-        <v>1.844722592099423</v>
+        <v>1.82116674170415</v>
       </c>
       <c r="H18">
         <v>100</v>
       </c>
       <c r="I18">
-        <v>77.22942606352436</v>
+        <v>76.82844899079002</v>
       </c>
       <c r="J18">
-        <v>55.57154280818965</v>
+        <v>55.18088410006043</v>
       </c>
       <c r="K18">
-        <v>42.7859106479081</v>
+        <v>41.55850243076583</v>
       </c>
       <c r="L18">
-        <v>30.61119414168124</v>
+        <v>29.55610010043041</v>
       </c>
       <c r="M18">
-        <v>19.52675669331749</v>
+        <v>18.53469098744901</v>
       </c>
       <c r="N18">
         <v>100</v>
       </c>
       <c r="O18">
-        <v>67.59215752526666</v>
+        <v>67.70117260300759</v>
       </c>
       <c r="P18">
-        <v>35.87970906607959</v>
+        <v>36.06891235898954</v>
       </c>
       <c r="Q18">
-        <v>12.10370108352295</v>
+        <v>12.19945337303406</v>
       </c>
       <c r="R18">
-        <v>2.756797755873849</v>
+        <v>2.784009022574768</v>
       </c>
       <c r="S18">
         <v>0</v>
@@ -1544,16 +1544,16 @@
         <v>100</v>
       </c>
       <c r="U18">
-        <v>61.57873649550234</v>
+        <v>60.32134453781512</v>
       </c>
       <c r="V18">
-        <v>37.46972900590587</v>
+        <v>36.49966386554622</v>
       </c>
       <c r="W18">
-        <v>19.26097999425604</v>
+        <v>18.82733893557423</v>
       </c>
       <c r="X18">
-        <v>4.24455772142294</v>
+        <v>4.466330532212885</v>
       </c>
       <c r="Y18">
         <v>0</v>
@@ -1567,52 +1567,52 @@
         <v>100</v>
       </c>
       <c r="C19">
-        <v>56.15690115819311</v>
+        <v>56.09468584037596</v>
       </c>
       <c r="D19">
-        <v>28.59315823215279</v>
+        <v>28.6967982386458</v>
       </c>
       <c r="E19">
-        <v>9.607157268890198</v>
+        <v>9.5486118366752</v>
       </c>
       <c r="F19">
-        <v>3.069321347331014</v>
+        <v>3.051345154028799</v>
       </c>
       <c r="G19">
-        <v>0.9752839550065248</v>
+        <v>0.9652624909237959</v>
       </c>
       <c r="H19">
         <v>100</v>
       </c>
       <c r="I19">
-        <v>78.00527414935556</v>
+        <v>77.3721096131396</v>
       </c>
       <c r="J19">
-        <v>57.5138825919282</v>
+        <v>56.84693143811915</v>
       </c>
       <c r="K19">
-        <v>38.8899347867419</v>
+        <v>38.12733850261741</v>
       </c>
       <c r="L19">
-        <v>23.57684205642402</v>
+        <v>22.82106174549302</v>
       </c>
       <c r="M19">
-        <v>11.89157533061775</v>
+        <v>11.19540169288829</v>
       </c>
       <c r="N19">
         <v>100</v>
       </c>
       <c r="O19">
-        <v>66.03781189872105</v>
+        <v>66.23277662692021</v>
       </c>
       <c r="P19">
-        <v>33.06625298281521</v>
+        <v>33.36696734549064</v>
       </c>
       <c r="Q19">
-        <v>10.01630987588895</v>
+        <v>10.27182585698124</v>
       </c>
       <c r="R19">
-        <v>1.855275899538371</v>
+        <v>1.95277587788011</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -1621,16 +1621,16 @@
         <v>100</v>
       </c>
       <c r="U19">
-        <v>55.93864659553341</v>
+        <v>55.46538439971476</v>
       </c>
       <c r="V19">
-        <v>30.00047469450918</v>
+        <v>29.86970970009385</v>
       </c>
       <c r="W19">
-        <v>12.29171010603089</v>
+        <v>12.53871807666754</v>
       </c>
       <c r="X19">
-        <v>1.844664323036746</v>
+        <v>1.947489307676666</v>
       </c>
       <c r="Y19">
         <v>0</v>
@@ -1644,37 +1644,37 @@
         <v>100</v>
       </c>
       <c r="C20">
-        <v>64.40159449436895</v>
+        <v>64.57077251022703</v>
       </c>
       <c r="D20">
-        <v>38.04956659569755</v>
+        <v>37.97407041373913</v>
       </c>
       <c r="E20">
-        <v>29.80093073260208</v>
+        <v>29.73639700399661</v>
       </c>
       <c r="F20">
-        <v>17.7231174591994</v>
+        <v>17.67936996410508</v>
       </c>
       <c r="G20">
-        <v>1.551155432723031</v>
+        <v>1.54555086727013</v>
       </c>
       <c r="H20">
         <v>100</v>
       </c>
       <c r="I20">
-        <v>86.01473865240494</v>
+        <v>85.78157934091352</v>
       </c>
       <c r="J20">
-        <v>72.07532446767185</v>
+        <v>71.63621227872545</v>
       </c>
       <c r="K20">
-        <v>50.93943520348972</v>
+        <v>50.43007476270706</v>
       </c>
       <c r="L20">
-        <v>20.70447928470168</v>
+        <v>20.56860683260243</v>
       </c>
       <c r="M20">
-        <v>10.66078842106725</v>
+        <v>9.980461104889033</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -1685,37 +1685,37 @@
         <v>100</v>
       </c>
       <c r="C21">
-        <v>67.00216098321665</v>
+        <v>66.8493477200973</v>
       </c>
       <c r="D21">
-        <v>43.43880326493974</v>
+        <v>43.26355110573506</v>
       </c>
       <c r="E21">
-        <v>25.36991276212722</v>
+        <v>25.2359103377625</v>
       </c>
       <c r="F21">
-        <v>1.635318360853074</v>
+        <v>1.625703338432391</v>
       </c>
       <c r="G21">
-        <v>0.05680539290782519</v>
+        <v>0.05616528386525391</v>
       </c>
       <c r="H21">
         <v>100</v>
       </c>
       <c r="I21">
-        <v>68.19607549074654</v>
+        <v>67.18035808852927</v>
       </c>
       <c r="J21">
-        <v>32.77466613610397</v>
+        <v>32.8606451249784</v>
       </c>
       <c r="K21">
-        <v>9.969284985328095</v>
+        <v>9.567623381181271</v>
       </c>
       <c r="L21">
-        <v>3.271829684277742</v>
+        <v>3.010763394421842</v>
       </c>
       <c r="M21">
-        <v>1.418930743604703</v>
+        <v>1.253599791570874</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -1726,52 +1726,52 @@
         <v>100</v>
       </c>
       <c r="C22">
-        <v>64.40159449436895</v>
+        <v>64.57077251022703</v>
       </c>
       <c r="D22">
-        <v>38.04956659569755</v>
+        <v>37.97407041373913</v>
       </c>
       <c r="E22">
-        <v>29.80093073260208</v>
+        <v>29.73639700399661</v>
       </c>
       <c r="F22">
-        <v>16.45792679477229</v>
+        <v>16.40448074476348</v>
       </c>
       <c r="G22">
-        <v>0.1522278578747831</v>
+        <v>0.1571077003034735</v>
       </c>
       <c r="H22">
         <v>100</v>
       </c>
       <c r="I22">
-        <v>84.22002807812869</v>
+        <v>83.96350420369055</v>
       </c>
       <c r="J22">
-        <v>68.68780902659472</v>
+        <v>68.19400517590289</v>
       </c>
       <c r="K22">
-        <v>53.94135627755039</v>
+        <v>53.18978740224767</v>
       </c>
       <c r="L22">
-        <v>21.924618700145</v>
+        <v>21.69419398512537</v>
       </c>
       <c r="M22">
-        <v>11.28904127270294</v>
+        <v>10.52662735170122</v>
       </c>
       <c r="N22">
         <v>100</v>
       </c>
       <c r="O22">
-        <v>65.91742491327362</v>
+        <v>66.07454575685048</v>
       </c>
       <c r="P22">
-        <v>31.46786278942648</v>
+        <v>31.59609169423096</v>
       </c>
       <c r="Q22">
-        <v>8.848003657161357</v>
+        <v>8.886342535859852</v>
       </c>
       <c r="R22">
-        <v>1.98561605053762</v>
+        <v>2.008774784249126</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -1780,16 +1780,16 @@
         <v>100</v>
       </c>
       <c r="U22">
-        <v>35.62691492628004</v>
+        <v>35.7225932021014</v>
       </c>
       <c r="V22">
-        <v>19.95098218138954</v>
+        <v>18.44667779606304</v>
       </c>
       <c r="W22">
-        <v>10.5861740980657</v>
+        <v>9.776627476422558</v>
       </c>
       <c r="X22">
-        <v>2.289430573119856</v>
+        <v>2.23184616114944</v>
       </c>
       <c r="Y22">
         <v>0</v>
@@ -1803,52 +1803,52 @@
         <v>100</v>
       </c>
       <c r="C23">
-        <v>65.88012724994734</v>
+        <v>65.6931837422526</v>
       </c>
       <c r="D23">
-        <v>41.25460213630802</v>
+        <v>41.06993042692174</v>
       </c>
       <c r="E23">
-        <v>26.14960972267349</v>
+        <v>25.98092390344646</v>
       </c>
       <c r="F23">
-        <v>2.277270479489347</v>
+        <v>2.262621849627246</v>
       </c>
       <c r="G23">
-        <v>0.005014232581663605</v>
+        <v>0.005150479860330742</v>
       </c>
       <c r="H23">
         <v>100</v>
       </c>
       <c r="I23">
-        <v>73.23513147311169</v>
+        <v>71.05005713041449</v>
       </c>
       <c r="J23">
-        <v>36.96732383273326</v>
+        <v>35.95147650282784</v>
       </c>
       <c r="K23">
-        <v>15.61832998984985</v>
+        <v>15.20956294028811</v>
       </c>
       <c r="L23">
-        <v>5.935092258000421</v>
+        <v>5.736939713383526</v>
       </c>
       <c r="M23">
-        <v>2.232023589512793</v>
+        <v>2.058132317926697</v>
       </c>
       <c r="N23">
         <v>100</v>
       </c>
       <c r="O23">
-        <v>64.75737862247892</v>
+        <v>64.92949133338472</v>
       </c>
       <c r="P23">
-        <v>24.51315756560022</v>
+        <v>24.68875026024467</v>
       </c>
       <c r="Q23">
-        <v>0.6940021941528592</v>
+        <v>0.753525664299404</v>
       </c>
       <c r="R23">
-        <v>0.05354019061467261</v>
+        <v>0.06292199732789081</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -1857,16 +1857,16 @@
         <v>100</v>
       </c>
       <c r="U23">
-        <v>22.78575610600391</v>
+        <v>21.58336521695477</v>
       </c>
       <c r="V23">
-        <v>2.993551500609445</v>
+        <v>3.789966430773744</v>
       </c>
       <c r="W23">
-        <v>1.588405845946939</v>
+        <v>1.691507731073679</v>
       </c>
       <c r="X23">
-        <v>0.3435183541728213</v>
+        <v>0.2783938794047403</v>
       </c>
       <c r="Y23">
         <v>0</v>
@@ -1880,37 +1880,37 @@
         <v>100</v>
       </c>
       <c r="C24">
-        <v>53.32606125166445</v>
+        <v>53.04880101321642</v>
       </c>
       <c r="D24">
-        <v>30.99747536617843</v>
+        <v>30.74628634584285</v>
       </c>
       <c r="E24">
-        <v>21.24831069684864</v>
+        <v>21.07333581588186</v>
       </c>
       <c r="F24">
-        <v>12.63672969374168</v>
+        <v>12.52886488624458</v>
       </c>
       <c r="G24">
-        <v>1.844722592099423</v>
+        <v>1.82116674170415</v>
       </c>
       <c r="H24">
         <v>100</v>
       </c>
       <c r="I24">
-        <v>86.01473865240494</v>
+        <v>85.78157934091352</v>
       </c>
       <c r="J24">
-        <v>72.07532446767185</v>
+        <v>71.63621227872545</v>
       </c>
       <c r="K24">
-        <v>50.93943520348972</v>
+        <v>50.43007476270706</v>
       </c>
       <c r="L24">
-        <v>20.70447928470168</v>
+        <v>20.56860683260243</v>
       </c>
       <c r="M24">
-        <v>11.05331370081376</v>
+        <v>10.73900547892924</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -1921,37 +1921,37 @@
         <v>100</v>
       </c>
       <c r="C25">
-        <v>60.90009866109576</v>
+        <v>60.76295060298562</v>
       </c>
       <c r="D25">
-        <v>34.22440189789863</v>
+        <v>34.19564684523031</v>
       </c>
       <c r="E25">
-        <v>15.99028679961251</v>
+        <v>15.89665832563523</v>
       </c>
       <c r="F25">
-        <v>1.955320688932531</v>
+        <v>1.944319085065449</v>
       </c>
       <c r="G25">
-        <v>0.339454578124826</v>
+        <v>0.3359582212498782</v>
       </c>
       <c r="H25">
         <v>100</v>
       </c>
       <c r="I25">
-        <v>69.73248637961505</v>
+        <v>68.78599498988203</v>
       </c>
       <c r="J25">
-        <v>38.14723604915922</v>
+        <v>37.82052013921835</v>
       </c>
       <c r="K25">
-        <v>16.79767166166855</v>
+        <v>16.0589558510581</v>
       </c>
       <c r="L25">
-        <v>7.640985096547352</v>
+        <v>7.133948893460619</v>
       </c>
       <c r="M25">
-        <v>3.407255752114068</v>
+        <v>3.067752657146357</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -1962,52 +1962,52 @@
         <v>100</v>
       </c>
       <c r="C26">
-        <v>53.32606125166445</v>
+        <v>53.04880101321642</v>
       </c>
       <c r="D26">
-        <v>30.99747536617843</v>
+        <v>30.74628634584285</v>
       </c>
       <c r="E26">
-        <v>21.24831069684864</v>
+        <v>21.07333581588186</v>
       </c>
       <c r="F26">
-        <v>11.73463826009765</v>
+        <v>11.62538728458281</v>
       </c>
       <c r="G26">
-        <v>1.844722592099423</v>
+        <v>1.82116674170415</v>
       </c>
       <c r="H26">
         <v>100</v>
       </c>
       <c r="I26">
-        <v>84.22002807812869</v>
+        <v>83.96350420369055</v>
       </c>
       <c r="J26">
-        <v>68.68780902659472</v>
+        <v>68.19400517590289</v>
       </c>
       <c r="K26">
-        <v>53.94135627755039</v>
+        <v>53.18978740224767</v>
       </c>
       <c r="L26">
-        <v>21.924618700145</v>
+        <v>21.69419398512537</v>
       </c>
       <c r="M26">
-        <v>11.70469853074221</v>
+        <v>11.32668196554458</v>
       </c>
       <c r="N26">
         <v>100</v>
       </c>
       <c r="O26">
-        <v>67.59215752526666</v>
+        <v>67.70117260300759</v>
       </c>
       <c r="P26">
-        <v>35.87970906607959</v>
+        <v>36.06891235898954</v>
       </c>
       <c r="Q26">
-        <v>12.10370108352295</v>
+        <v>12.19945337303406</v>
       </c>
       <c r="R26">
-        <v>2.756797755873849</v>
+        <v>2.784009022574768</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -2016,16 +2016,16 @@
         <v>100</v>
       </c>
       <c r="U26">
-        <v>61.57873649550234</v>
+        <v>60.32134453781512</v>
       </c>
       <c r="V26">
-        <v>37.46972900590587</v>
+        <v>36.49966386554622</v>
       </c>
       <c r="W26">
-        <v>19.26097999425604</v>
+        <v>18.82733893557423</v>
       </c>
       <c r="X26">
-        <v>4.24455772142294</v>
+        <v>4.466330532212885</v>
       </c>
       <c r="Y26">
         <v>0</v>
@@ -2039,52 +2039,52 @@
         <v>100</v>
       </c>
       <c r="C27">
-        <v>60.18908642639378</v>
+        <v>60.07288637969662</v>
       </c>
       <c r="D27">
-        <v>33.8438189393469</v>
+        <v>33.82496878045952</v>
       </c>
       <c r="E27">
-        <v>16.46726167914202</v>
+        <v>16.35915780089444</v>
       </c>
       <c r="F27">
-        <v>2.740859625918509</v>
+        <v>2.724450566205944</v>
       </c>
       <c r="G27">
-        <v>0.5729157936650942</v>
+        <v>0.5673339110093446</v>
       </c>
       <c r="H27">
         <v>100</v>
       </c>
       <c r="I27">
-        <v>75.01150486659989</v>
+        <v>73.39495427050005</v>
       </c>
       <c r="J27">
-        <v>44.61870100102481</v>
+        <v>43.70177298480334</v>
       </c>
       <c r="K27">
-        <v>24.28449908719795</v>
+        <v>23.70995211605734</v>
       </c>
       <c r="L27">
-        <v>12.50474486540395</v>
+        <v>12.07358329096674</v>
       </c>
       <c r="M27">
-        <v>5.829166684821043</v>
+        <v>5.447221262147586</v>
       </c>
       <c r="N27">
         <v>100</v>
       </c>
       <c r="O27">
-        <v>65.68127706951169</v>
+        <v>65.8744534118585</v>
       </c>
       <c r="P27">
-        <v>30.68469581658076</v>
+        <v>30.98104443303462</v>
       </c>
       <c r="Q27">
-        <v>7.420569293164739</v>
+        <v>7.654935649749528</v>
       </c>
       <c r="R27">
-        <v>1.35359371859724</v>
+        <v>1.433193652336163</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -2093,16 +2093,16 @@
         <v>100</v>
       </c>
       <c r="U27">
-        <v>54.2242129487852</v>
+        <v>53.72899910977861</v>
       </c>
       <c r="V27">
-        <v>28.60386762327898</v>
+        <v>28.53317565928563</v>
       </c>
       <c r="W27">
-        <v>11.73821195776271</v>
+        <v>11.98282280037234</v>
       </c>
       <c r="X27">
-        <v>1.76703577920047</v>
+        <v>1.861951708579153</v>
       </c>
       <c r="Y27">
         <v>0</v>
@@ -2116,37 +2116,37 @@
         <v>100</v>
       </c>
       <c r="C28">
-        <v>79.32756588170562</v>
+        <v>79.3924080523969</v>
       </c>
       <c r="D28">
-        <v>60.70552086417366</v>
+        <v>60.66077156289573</v>
       </c>
       <c r="E28">
-        <v>52.95970286932803</v>
+        <v>52.80263968782018</v>
       </c>
       <c r="F28">
-        <v>49.54928053874312</v>
+        <v>49.37631825299975</v>
       </c>
       <c r="G28">
-        <v>47.75392266473074</v>
+        <v>47.5737691376413</v>
       </c>
       <c r="H28">
         <v>100</v>
       </c>
       <c r="I28">
-        <v>98.05571691107782</v>
+        <v>97.91821020612211</v>
       </c>
       <c r="J28">
-        <v>96.25129792117471</v>
+        <v>95.99743449247634</v>
       </c>
       <c r="K28">
-        <v>94.58476147124532</v>
+        <v>94.23638380073612</v>
       </c>
       <c r="L28">
-        <v>93.07291684359159</v>
+        <v>92.64893943148363</v>
       </c>
       <c r="M28">
-        <v>91.71246898860093</v>
+        <v>91.21998731656672</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2157,37 +2157,37 @@
         <v>100</v>
       </c>
       <c r="C29">
-        <v>72.0742546444441</v>
+        <v>72.22104281487756</v>
       </c>
       <c r="D29">
-        <v>47.33308673253634</v>
+        <v>47.3408410355703</v>
       </c>
       <c r="E29">
-        <v>37.59063392514427</v>
+        <v>37.47082412961763</v>
       </c>
       <c r="F29">
-        <v>33.85592139320776</v>
+        <v>33.72237193304118</v>
       </c>
       <c r="G29">
-        <v>31.97559999739768</v>
+        <v>31.84241333660199</v>
       </c>
       <c r="H29">
         <v>100</v>
       </c>
       <c r="I29">
-        <v>98.03111448173276</v>
+        <v>97.89000429668766</v>
       </c>
       <c r="J29">
-        <v>96.03811777087758</v>
+        <v>95.801496192692</v>
       </c>
       <c r="K29">
-        <v>94.1441593313118</v>
+        <v>93.79845580557567</v>
       </c>
       <c r="L29">
-        <v>92.44202793367833</v>
+        <v>91.99887352384063</v>
       </c>
       <c r="M29">
-        <v>90.89690373635641</v>
+        <v>90.36058139019109</v>
       </c>
     </row>
   </sheetData>
